--- a/diseases/d085/2005-2009.xlsx
+++ b/diseases/d085/2005-2009.xlsx
@@ -12396,17 +12396,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -12440,100 +12440,28 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="O54" t="n">
+        <v>266</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.4215099172964265</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Toxóplasmasýking</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN54" t="b">
-        <v>0</v>
+          <t>annual</t>
+        </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -12552,11 +12480,11 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
@@ -12565,42 +12493,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12632,12 +12560,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -12662,50 +12590,53 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="O55" t="n">
+        <v>266</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
+          <t>SRC_FR_ECDC_ATLAS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Toxóplasmasýking</t>
+          <t>Toxoplasmosis, congenital</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>registered_diagnoses</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>primary_care_icd_registered_diagnoses</t>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -12715,7 +12646,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:FR:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -12725,12 +12656,12 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>not_comparable</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -12740,7 +12671,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
@@ -12750,12 +12681,12 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -12764,7 +12695,7 @@
         </is>
       </c>
       <c r="AN55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -12783,11 +12714,11 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -12796,42 +12727,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -12858,17 +12789,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -12893,93 +12824,176 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
         <v>2</v>
       </c>
-      <c r="O56" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.008633952820887223</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -13041,12 +13055,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -13272,25 +13286,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.004316976410443612</v>
+        <v>0.008633952820887223</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -13420,12 +13434,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -13616,17 +13630,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -13651,176 +13665,93 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0</v>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Toxóplasmasýking</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN60" t="b">
+      <c r="R60" t="n">
+        <v>0.004316976410443612</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT60" t="n">
-        <v>2</v>
-      </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13882,12 +13813,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -14078,17 +14009,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -14113,93 +14044,176 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="n">
         <v>0</v>
       </c>
-      <c r="R62" t="n">
-        <v>0.004316976410443612</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN62" t="b">
+        <v>0</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -14261,12 +14275,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -14492,12 +14506,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -14640,12 +14654,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -14836,17 +14850,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -14871,176 +14885,93 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0</v>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_LEGACY_ICD</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Toxóplasmasýking</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>primary_care_icd_registered_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>IS_DOH_legacy_ICD_monthly</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN66" t="b">
+      <c r="R66" t="n">
+        <v>0.004316976410443612</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP66" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AT66" t="n">
-        <v>2</v>
-      </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15102,12 +15033,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -15298,17 +15229,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -15333,93 +15264,176 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q68" t="n">
         <v>0</v>
       </c>
-      <c r="R68" t="n">
-        <v>0.004316976410443612</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN68" t="b">
+        <v>0</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -15481,12 +15495,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -15712,12 +15726,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -15860,12 +15874,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -16028,6 +16042,385 @@
         </is>
       </c>
       <c r="BC71" t="inlineStr">
+        <is>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.004316976410443612</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_IS_LEGACY_ICD_B58_TOXOPLASMASYKING_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_LEGACY_ICD</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Toxóplasmasýking</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>primary_care_icd_registered_diagnoses</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>IS_DOH_legacy_ICD_monthly</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Iceland historical primary-care registered diagnoses for ICD-10 B58; this reporting basis is not interchangeable with national notification counts. Published dashes are explicit zero and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_TOXOPLASMOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>is_doh_annual</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
         <is>
           <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
@@ -16149,7 +16542,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -16159,7 +16552,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -16179,7 +16572,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -16189,7 +16582,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -16211,7 +16604,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16">
